--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Ra1e95ffa0835403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rdb02bc131ebe4f4f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -130,6 +130,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CARLOS  SANTO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.20817843866171004</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>331</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -177,7 +190,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.088908845981140683</x:v>
+        <x:v>0.15909490512192814</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -203,7 +216,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.084288052373158839</x:v>
+        <x:v>0.17338273892234057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -216,7 +229,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.14049909020015594</x:v>
+        <x:v>0.14948761047551917</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -242,7 +255,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.20505772402418909</x:v>
+        <x:v>0.17535958157780018</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ISMAEL  SIQUEIRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.18034586878945924</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -268,7 +294,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.079526353143326789</x:v>
+        <x:v>0.19428181458999338</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +320,33 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.032369974540469526</x:v>
+        <x:v>0.077048396064183233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JOSE  RIQUELME</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.22168601365158036</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JUNIOR  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.34730538922155696</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -333,7 +385,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.15341856586992786</x:v>
+        <x:v>0.1897572170552</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -385,7 +437,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.35823429541595919</x:v>
+        <x:v>0.24698310539018498</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -398,7 +450,33 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.40120329322355919</x:v>
+        <x:v>0.24028505450301707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIY  OLIVEIRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.32108513318381515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REGIANDRO  MOREIRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.87106297166379076</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -412,6 +490,19 @@
       </x:c>
       <x:c s="9">
         <x:v>0.58279220779220786</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ROWILSON  PEREIRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.40503875968992253</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -448,7 +539,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.16667691459377543</x:v>
+        <x:v>0.24000826901874306</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -460,7 +551,7 @@
 Revenda é GranDourados
 Frota é Padronizada
 Ano é 2026
-Date é igual a ou está depois de 01/09/2026 e está antes de 04/09/2026
+Date é igual a ou está depois de 01/09/2026 e está antes de 06/09/2026
 Taxa de Dispersão é Até 100%
 Check Dispersão KM é Sim
 Tipo Dispersão KM é Positiva

--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rdb02bc131ebe4f4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Re3194d285d824ffb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -164,7 +164,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.15888478333893175</x:v>
+        <x:v>0.17306419589675714</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -229,7 +229,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.14948761047551917</x:v>
+        <x:v>0.11487027735107591</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -385,7 +385,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.1897572170552</x:v>
+        <x:v>0.17521754566466452</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -450,7 +450,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.24028505450301707</x:v>
+        <x:v>0.25238420844279696</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -494,6 +494,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RILLER  GIMENEZ</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.25566120758118882</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>288</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -502,7 +515,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.40503875968992253</x:v>
+        <x:v>0.48863719134678418</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -515,7 +528,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.10232183402915118</x:v>
+        <x:v>0.10616535656785664</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -539,7 +552,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.24000826901874306</x:v>
+        <x:v>0.24332298639868921</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -551,7 +564,7 @@
 Revenda é GranDourados
 Frota é Padronizada
 Ano é 2026
-Date é igual a ou está depois de 01/09/2026 e está antes de 06/09/2026
+Date é igual a ou está depois de 01/09/2026 e está antes de 09/09/2026
 Taxa de Dispersão é Até 100%
 Check Dispersão KM é Sim
 Tipo Dispersão KM é Positiva

--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Re3194d285d824ffb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R09288a09d67046c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -125,20 +125,20 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.083634342873020184</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>CARLOS  SANTO</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.20817843866171004</x:v>
+        <x:v>0.076830006049606769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BRUNO  LEITE</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.51561079114883279</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -156,19 +156,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ELIZEU  SILVA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.17306419589675714</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>27</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -177,20 +164,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.32297958009778527</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>GEFERSON  QUADRA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.15909490512192814</x:v>
+        <x:v>0.22826386972122537</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -208,32 +182,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>GEOVANE  SILVA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.17338273892234057</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>GUSTAVO  SILVA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.11487027735107591</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>146</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -247,19 +195,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HELTON  CAVALHEIRO</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.17535958157780018</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>350</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -286,67 +221,15 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>JETERSON  MALDONADO</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.19428181458999338</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>JOÃO  LUNELLI</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.1787085159142634</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>JOAO  SILVA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.077048396064183233</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>JOSE  RIQUELME</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.22168601365158036</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>JUNIOR  SILVA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.34730538922155696</x:v>
+        <x:v>453</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JOSUE  ESTEMBERG</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.30344108446298224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -359,7 +242,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.44974751588206541</x:v>
+        <x:v>0.36676499508357918</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -377,19 +260,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>689</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>LUCAS  SILVA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.17521754566466452</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>285</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -416,19 +286,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>732</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MARIO  MELCHIOR</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.17411524264353195</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>2</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -442,32 +299,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MAURO  CACERES</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.25238420844279696</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIY  OLIVEIRA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.32108513318381515</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>16</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -476,7 +307,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.87106297166379076</x:v>
+        <x:v>0.8369095292172215</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,46 +320,7 @@
         </x:is>
       </x:c>
       <x:c s="9">
-        <x:v>0.58279220779220786</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RILLER  GIMENEZ</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.25566120758118882</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ROWILSON  PEREIRA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.48863719134678418</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>960</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>VALDECI  MARINS</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.10616535656785664</x:v>
+        <x:v>0.74441395531164267</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -552,7 +344,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.24332298639868921</x:v>
+        <x:v>0.417772551654628</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -564,8 +356,9 @@
 Revenda é GranDourados
 Frota é Padronizada
 Ano é 2026
-Date é igual a ou está depois de 01/09/2026 e está antes de 09/09/2026
+Date é igual a ou está depois de 01/09/2026 e está antes de 10/09/2026
 Taxa de Dispersão é Até 100%
+Supervisor não é 2
 Check Dispersão KM é Sim
 Tipo Dispersão KM é Positiva
 Meta Dispersão KM é 20

--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R09288a09d67046c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R01c315de89af4bc5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -143,6 +143,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CARLOS  SANTO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.1674710864220017</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>331</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -156,6 +169,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ELIZEU  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.17306419589675714</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>27</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -169,6 +195,32 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>718</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EMERSON  SANTOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.46249832282302417</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GEFERSON  QUADRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.41816966027081737</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>544</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -182,6 +234,32 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GEOVANE  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.17338273892234057</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GUSTAVO  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.11487027735107591</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>146</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -195,6 +273,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HELTON  CAVALHEIRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.17507720164200746</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>350</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -221,6 +312,58 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JETERSON  MALDONADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.19428181458999338</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JOÃO  LUNELLI</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.1787085159142634</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JOAO  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.077048396064183233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JOSE  RIQUELME</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.15309987988542928</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>453</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -234,6 +377,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JUNIOR  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.34730538922155696</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>313</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -260,6 +416,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LUCAS  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.17521754566466452</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>285</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -286,6 +455,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MARIO  MELCHIOR</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.088763049730794963</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>2</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -299,6 +481,45 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MAURO  CACERES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.21293609794069779</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NEIMAN  SANTOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.12342259156663582</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIY  OLIVEIRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.32108513318381515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>16</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -321,6 +542,45 @@
       </x:c>
       <x:c s="9">
         <x:v>0.74441395531164267</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RILLER  GIMENEZ</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.1503649635036497</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ROWILSON  PEREIRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.48863719134678418</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>960</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VALDECI  MARINS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.10616535656785664</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -344,7 +604,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.417772551654628</x:v>
+        <x:v>0.23698995635056974</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -358,7 +618,6 @@
 Ano é 2026
 Date é igual a ou está depois de 01/09/2026 e está antes de 10/09/2026
 Taxa de Dispersão é Até 100%
-Supervisor não é 2
 Check Dispersão KM é Sim
 Tipo Dispersão KM é Positiva
 Meta Dispersão KM é 20

--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R01c315de89af4bc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Raef09714122e4871"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -143,19 +143,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>CARLOS  SANTO</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.1674710864220017</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>331</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -169,19 +156,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ELIZEU  SILVA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.17306419589675714</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>27</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -195,32 +169,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>718</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>EMERSON  SANTOS</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.46249832282302417</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>GEFERSON  QUADRA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.41816966027081737</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>544</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -234,32 +182,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>GEOVANE  SILVA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.17338273892234057</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>GUSTAVO  SILVA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.11487027735107591</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>146</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -273,19 +195,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HELTON  CAVALHEIRO</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.17507720164200746</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>350</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -312,58 +221,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>JETERSON  MALDONADO</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.19428181458999338</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>JOÃO  LUNELLI</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.1787085159142634</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>JOAO  SILVA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.077048396064183233</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>JOSE  RIQUELME</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.15309987988542928</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>453</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -377,19 +234,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>JUNIOR  SILVA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.34730538922155696</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>313</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -416,19 +260,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>689</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>LUCAS  SILVA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.17521754566466452</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>285</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -455,19 +286,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>732</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MARIO  MELCHIOR</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.088763049730794963</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>2</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -481,45 +299,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MAURO  CACERES</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.21293609794069779</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NEIMAN  SANTOS</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.12342259156663582</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NIY  OLIVEIRA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.32108513318381515</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>16</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -546,45 +325,6 @@
     </x:row>
     <x:row>
       <x:c s="8">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>RILLER  GIMENEZ</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.1503649635036497</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>ROWILSON  PEREIRA</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.48863719134678418</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
-        <x:v>960</x:v>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>VALDECI  MARINS</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.10616535656785664</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="8">
         <x:v>302</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -594,6 +334,19 @@
       </x:c>
       <x:c s="9">
         <x:v>0.34911242603550297</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>YGOR  REIS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.22494432071269488</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -604,7 +357,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.23698995635056974</x:v>
+        <x:v>0.41585267149335325</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -616,8 +369,9 @@
 Revenda é GranDourados
 Frota é Padronizada
 Ano é 2026
-Date é igual a ou está depois de 01/09/2026 e está antes de 10/09/2026
+Date é igual a ou está depois de 01/09/2026 e está antes de 11/09/2026
 Taxa de Dispersão é Até 100%
+Supervisor não é 2
 Check Dispersão KM é Sim
 Tipo Dispersão KM é Positiva
 Meta Dispersão KM é 20

--- a/Dispersão KM por Motorista.xlsx
+++ b/Dispersão KM por Motorista.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Raef09714122e4871"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R0963e7c0761c46bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -143,6 +143,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CARLOS  SANTO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.15390847434087185</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>331</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -156,6 +169,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ELIZEU  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.17306419589675714</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>27</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -169,6 +195,32 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>718</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>EMERSON  SANTOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.46249832282302417</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GEFERSON  QUADRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.41816966027081737</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>544</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -182,6 +234,32 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GEOVANE  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.17338273892234057</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GUSTAVO  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.11487027735107591</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>146</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -195,6 +273,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HELTON  CAVALHEIRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.17507720164200746</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>350</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -221,6 +312,58 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JETERSON  MALDONADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.35085276299972645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JOÃO  LUNELLI</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.1787085159142634</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JOAO  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.052631578947368363</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JOSE  RIQUELME</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.14937962631920443</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>453</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -234,6 +377,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JUNIOR  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.346690508076402</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>313</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -260,6 +416,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LUCAS  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.24234912653751728</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>285</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -286,6 +455,19 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MARIO  MELCHIOR</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.088763049730794963</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>2</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -299,6 +481,45 @@
     </x:row>
     <x:row>
       <x:c s="8">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MAURO  CACERES</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.21293609794069779</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NEIMAN  SANTOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.12342259156663582</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NIY  OLIVEIRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.32108513318381515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
         <x:v>16</x:v>
       </x:c>
       <x:c t="inlineStr">
@@ -321,6 +542,58 @@
       </x:c>
       <x:c s="9">
         <x:v>0.74441395531164267</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RILLER  GIMENEZ</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.13083680658769348</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ROWILSON  PEREIRA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.48863719134678418</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>960</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VALDECI  MARINS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.14454218312674927</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VAUDENIR  SILVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.741620868488273</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -357,7 +630,7 @@
       </x:c>
       <x:c s="1"/>
       <x:c s="10">
-        <x:v>0.41585267149335325</x:v>
+        <x:v>0.25160836450567992</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -371,7 +644,6 @@
 Ano é 2026
 Date é igual a ou está depois de 01/09/2026 e está antes de 11/09/2026
 Taxa de Dispersão é Até 100%
-Supervisor não é 2
 Check Dispersão KM é Sim
 Tipo Dispersão KM é Positiva
 Meta Dispersão KM é 20
